--- a/data/H131_20260625_12.xlsx
+++ b/data/H131_20260625_12.xlsx
@@ -1436,10 +1436,10 @@
         <v>741.0</v>
       </c>
       <c r="O15" s="2">
-        <v>361.0</v>
+        <v>363.0</v>
       </c>
       <c r="P15" s="2">
-        <v>365.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q15" s="2">
         <v>15.0</v>
@@ -2457,7 +2457,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>1076.0</v>
+        <v>1117.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2469,34 +2469,34 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>1076.0</v>
+        <v>1117.0</v>
       </c>
       <c r="O29" s="2">
-        <v>425.0</v>
+        <v>434.0</v>
       </c>
       <c r="P29" s="2">
-        <v>422.0</v>
+        <v>427.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>229.0</v>
+        <v>256.0</v>
       </c>
       <c r="R29" s="2">
         <v>47.0</v>
       </c>
       <c r="S29" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="T29" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="U29" s="2">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="V29" s="2">
         <v>0.0</v>
       </c>
       <c r="W29" s="2">
-        <v>87.0</v>
+        <v>97.0</v>
       </c>
       <c r="X29" s="1">
         <v>1.0</v>
@@ -5133,7 +5133,7 @@
         <v>0.0</v>
       </c>
       <c r="N65" s="2">
-        <v>503.0</v>
+        <v>500.0</v>
       </c>
       <c r="O65" s="2">
         <v>290.0</v>
@@ -5269,7 +5269,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>1048.0</v>
+        <v>1049.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5281,7 +5281,7 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>1048.0</v>
+        <v>1049.0</v>
       </c>
       <c r="O67" s="2">
         <v>501.0</v>
@@ -5290,13 +5290,13 @@
         <v>511.0</v>
       </c>
       <c r="Q67" s="2">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="R67" s="2">
         <v>60.0</v>
       </c>
       <c r="S67" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="T67" s="2">
         <v>0.0</v>
@@ -5308,7 +5308,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>81.0</v>
+        <v>80.0</v>
       </c>
       <c r="X67" s="1">
         <v>1.0</v>
@@ -5417,7 +5417,7 @@
         <v>1125.0</v>
       </c>
       <c r="J69" s="2">
-        <v>1115.0</v>
+        <v>1114.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5429,10 +5429,10 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>1114.0</v>
+        <v>1113.0</v>
       </c>
       <c r="O69" s="2">
-        <v>608.0</v>
+        <v>607.0</v>
       </c>
       <c r="P69" s="2">
         <v>496.0</v>
@@ -5447,7 +5447,7 @@
         <v>2.0</v>
       </c>
       <c r="T69" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U69" s="2">
         <v>0.0</v>
@@ -5456,7 +5456,7 @@
         <v>0.0</v>
       </c>
       <c r="W69" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="X69" s="1">
         <v>1.0</v>
@@ -8303,7 +8303,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>897.0</v>
+        <v>898.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -8315,10 +8315,10 @@
         <v>0.0</v>
       </c>
       <c r="N108" s="2">
-        <v>897.0</v>
+        <v>898.0</v>
       </c>
       <c r="O108" s="2">
-        <v>565.0</v>
+        <v>566.0</v>
       </c>
       <c r="P108" s="2">
         <v>332.0</v>
@@ -10686,10 +10686,10 @@
         <v>1118.0</v>
       </c>
       <c r="O140" s="2">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="P140" s="2">
-        <v>490.0</v>
+        <v>489.0</v>
       </c>
       <c r="Q140" s="2">
         <v>24.0</v>
@@ -11189,7 +11189,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>1166.0</v>
+        <v>1205.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -11201,16 +11201,16 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>1166.0</v>
+        <v>1205.0</v>
       </c>
       <c r="O147" s="2">
-        <v>600.0</v>
+        <v>619.0</v>
       </c>
       <c r="P147" s="2">
-        <v>553.0</v>
+        <v>572.0</v>
       </c>
       <c r="Q147" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R147" s="2">
         <v>9.0</v>
@@ -11263,7 +11263,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>1220.0</v>
+        <v>1224.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -11275,13 +11275,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>1220.0</v>
+        <v>1224.0</v>
       </c>
       <c r="O148" s="2">
-        <v>628.0</v>
+        <v>630.0</v>
       </c>
       <c r="P148" s="2">
-        <v>574.0</v>
+        <v>576.0</v>
       </c>
       <c r="Q148" s="2">
         <v>18.0</v>
@@ -11337,7 +11337,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>1124.0</v>
+        <v>1131.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -11349,19 +11349,19 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>1124.0</v>
+        <v>1131.0</v>
       </c>
       <c r="O149" s="2">
-        <v>668.0</v>
+        <v>672.0</v>
       </c>
       <c r="P149" s="2">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="Q149" s="2">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="R149" s="2">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="S149" s="2">
         <v>5.0</v>
@@ -11376,7 +11376,7 @@
         <v>0.0</v>
       </c>
       <c r="W149" s="2">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="X149" s="1">
         <v>1.0</v>
@@ -11929,7 +11929,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>1387.0</v>
+        <v>1391.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11941,13 +11941,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>1383.0</v>
+        <v>1387.0</v>
       </c>
       <c r="O157" s="2">
-        <v>719.0</v>
+        <v>722.0</v>
       </c>
       <c r="P157" s="2">
-        <v>639.0</v>
+        <v>640.0</v>
       </c>
       <c r="Q157" s="2">
         <v>29.0</v>
@@ -13409,7 +13409,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>934.0</v>
+        <v>939.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -13421,13 +13421,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>934.0</v>
+        <v>939.0</v>
       </c>
       <c r="O177" s="2">
-        <v>551.0</v>
+        <v>554.0</v>
       </c>
       <c r="P177" s="2">
-        <v>383.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -13557,7 +13557,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>974.0</v>
+        <v>976.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13569,10 +13569,10 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>974.0</v>
+        <v>976.0</v>
       </c>
       <c r="O179" s="2">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="P179" s="2">
         <v>378.0</v>
@@ -13581,7 +13581,7 @@
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
       <c r="S179" s="2">
         <v>14.0</v>
@@ -13596,7 +13596,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="X179" s="1">
         <v>1.0</v>
@@ -14756,13 +14756,13 @@
         <v>538.0</v>
       </c>
       <c r="O195" s="2">
-        <v>266.0</v>
+        <v>306.0</v>
       </c>
       <c r="P195" s="2">
         <v>213.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>59.0</v>
+        <v>19.0</v>
       </c>
       <c r="R195" s="2">
         <v>13.0</v>
@@ -14830,13 +14830,13 @@
         <v>1307.0</v>
       </c>
       <c r="O196" s="2">
-        <v>572.0</v>
+        <v>587.0</v>
       </c>
       <c r="P196" s="2">
-        <v>545.0</v>
+        <v>544.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>190.0</v>
+        <v>176.0</v>
       </c>
       <c r="R196" s="2">
         <v>38.0</v>
@@ -15777,7 +15777,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>841.0</v>
+        <v>840.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15789,19 +15789,19 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>841.0</v>
+        <v>840.0</v>
       </c>
       <c r="O209" s="2">
         <v>437.0</v>
       </c>
       <c r="P209" s="2">
-        <v>404.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
       </c>
       <c r="R209" s="2">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="S209" s="2">
         <v>56.0</v>
@@ -15816,7 +15816,7 @@
         <v>1.0</v>
       </c>
       <c r="W209" s="2">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="X209" s="1">
         <v>1.0</v>
@@ -16147,7 +16147,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>883.0</v>
+        <v>887.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -16159,13 +16159,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>883.0</v>
+        <v>887.0</v>
       </c>
       <c r="O214" s="2">
-        <v>472.0</v>
+        <v>473.0</v>
       </c>
       <c r="P214" s="2">
-        <v>411.0</v>
+        <v>414.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -16236,16 +16236,16 @@
         <v>1002.0</v>
       </c>
       <c r="O215" s="2">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
       <c r="P215" s="2">
-        <v>473.0</v>
+        <v>472.0</v>
       </c>
       <c r="Q215" s="2">
         <v>22.0</v>
       </c>
       <c r="R215" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S215" s="2">
         <v>21.0</v>
@@ -16254,7 +16254,7 @@
         <v>7.0</v>
       </c>
       <c r="U215" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="V215" s="2">
         <v>0.0</v>
@@ -16443,7 +16443,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>1059.0</v>
+        <v>1063.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -16455,10 +16455,10 @@
         <v>0.0</v>
       </c>
       <c r="N218" s="2">
-        <v>1059.0</v>
+        <v>1063.0</v>
       </c>
       <c r="O218" s="2">
-        <v>544.0</v>
+        <v>548.0</v>
       </c>
       <c r="P218" s="2">
         <v>515.0</v>
@@ -17109,7 +17109,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" s="2">
-        <v>408.0</v>
+        <v>412.0</v>
       </c>
       <c r="K227" s="2">
         <v>1.0</v>
@@ -17121,10 +17121,10 @@
         <v>0.0</v>
       </c>
       <c r="N227" s="2">
-        <v>408.0</v>
+        <v>412.0</v>
       </c>
       <c r="O227" s="2">
-        <v>261.0</v>
+        <v>265.0</v>
       </c>
       <c r="P227" s="2">
         <v>147.0</v>
